--- a/br-changemain-to-ci-buildstatus/ig/StructureDefinition-sas-sos-appointment.xlsx
+++ b/br-changemain-to-ci-buildstatus/ig/StructureDefinition-sas-sos-appointment.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-04T12:11:36+00:00</t>
+    <t>2024-07-04T12:27:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
